--- a/Gantt Mini Project.xlsx
+++ b/Gantt Mini Project.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Gestion du matériel informatique - Gantt Prévisionnel</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t xml:space="preserve">Finalisation du gantt et création du fichier répondant au questions </t>
+  </si>
+  <si>
+    <t>Création de la fiche recette</t>
   </si>
 </sst>
 </file>
@@ -63,7 +66,7 @@
     <numFmt numFmtId="164" formatCode="HH:mm:ss"/>
     <numFmt numFmtId="165" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -85,6 +88,11 @@
       <sz val="12.0"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -167,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -223,6 +231,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -947,6 +959,12 @@
       <c r="Q23" s="11"/>
       <c r="R23" s="11"/>
     </row>
+    <row r="25" ht="35.25" customHeight="1">
+      <c r="A25" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="22"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:R1"/>
